--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487455_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487455_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5195</v>
+        <v>5.5884</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6288</v>
+        <v>5.9649</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1092</v>
+        <v>-0.3766</v>
       </c>
       <c r="G2" t="n">
         <v>2.9382</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9938</v>
+        <v>0.0626</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2408</v>
+        <v>0.577</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.247</v>
+        <v>-0.5143</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9726</v>
+        <v>5.0543</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5916</v>
+        <v>7.4862</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.619</v>
+        <v>-2.4319</v>
       </c>
       <c r="G3" t="n">
         <v>0.1974</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.3619</v>
+        <v>-1.2802</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1704</v>
+        <v>-0.2758</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1915</v>
+        <v>-1.0044</v>
       </c>
       <c r="V3" t="n">
         <v>3.9828</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2418</v>
+        <v>3.1435</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8041</v>
+        <v>5.1869</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5623</v>
+        <v>-2.0435</v>
       </c>
       <c r="G4" t="n">
         <v>1.161</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1015</v>
+        <v>0.0032</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1317</v>
+        <v>0.2511</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2333</v>
+        <v>-0.2479</v>
       </c>
       <c r="V4" t="n">
         <v>0.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.417</v>
+        <v>2.8798</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7055</v>
+        <v>2.1149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7115</v>
+        <v>0.765</v>
       </c>
       <c r="G5" t="n">
         <v>2.675</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2373</v>
+        <v>0.2256</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3564</v>
+        <v>0.0529</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1192</v>
+        <v>0.1726</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7111</v>
+        <v>0.9822</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1178</v>
+        <v>0.3939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.829</v>
+        <v>0.5884</v>
       </c>
       <c r="G6" t="n">
         <v>1.1556</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.032</v>
+        <v>-0.7609</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.891</v>
+        <v>-0.3794</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.141</v>
+        <v>-0.3815</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.402</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3383</v>
+        <v>2.2164</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7403</v>
+        <v>-1.473</v>
       </c>
       <c r="G7" t="n">
         <v>0.094</v>
@@ -1000,13 +1000,13 @@
         <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6711</v>
+        <v>0.4743</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5764</v>
+        <v>0.3017</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.1726</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8655</v>
+        <v>-1.3308</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-1.411</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2138</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6696</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5507</v>
+        <v>0.0854</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9775</v>
+        <v>0.2182</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4268</v>
+        <v>-0.1328</v>
       </c>
       <c r="V8" t="n">
         <v>0.6659</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4085</v>
+        <v>-1.4676</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1907</v>
+        <v>-0.2766</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2177</v>
+        <v>-1.191</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5056</v>
@@ -1156,13 +1156,13 @@
         <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4156</v>
+        <v>-0.4748</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6099</v>
+        <v>0.524</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0255</v>
+        <v>-0.9988</v>
       </c>
       <c r="V9" t="n">
         <v>0.8837</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2054</v>
+        <v>-4.7216</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6261</v>
+        <v>-2.3026</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5793</v>
+        <v>-2.419</v>
       </c>
       <c r="G10" t="n">
         <v>0.9539</v>
@@ -1234,13 +1234,13 @@
         <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1421</v>
+        <v>-1.6582</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8316</v>
+        <v>-0.5082</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3105</v>
+        <v>-1.1501</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8837</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.980599999999999</v>
+        <v>10.8716</v>
       </c>
       <c r="E11" t="n">
-        <v>18.482</v>
+        <v>19.373</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.501100000000001</v>
+        <v>-8.5014</v>
       </c>
       <c r="G11" t="n">
         <v>5.9999</v>
@@ -1312,13 +1312,13 @@
         <v>13.7093</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.214</v>
+        <v>-3.323</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1292999999999999</v>
+        <v>0.7614999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.0845</v>
+        <v>-4.0846</v>
       </c>
       <c r="V11" t="n">
         <v>5.257</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.4901</v>
+        <v>8.3071</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5044</v>
+        <v>10.174</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0143</v>
+        <v>-1.8669</v>
       </c>
       <c r="G12" t="n">
         <v>6.1379</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0187</v>
+        <v>1.8357</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5731</v>
+        <v>1.2427</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4456</v>
+        <v>0.593</v>
       </c>
       <c r="V12" t="n">
         <v>1.3127</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2293</v>
+        <v>3.2471</v>
       </c>
       <c r="E13" t="n">
-        <v>3.014</v>
+        <v>3.628</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7847</v>
+        <v>-0.381</v>
       </c>
       <c r="G13" t="n">
         <v>0.876</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4093</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0641</v>
+        <v>0.6781</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4734</v>
+        <v>-0.0697</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.6965</v>
+        <v>-1.3047</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.4632</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0287</v>
+        <v>-0.8416</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1161</v>
@@ -1624,13 +1624,13 @@
         <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7775</v>
+        <v>-0.3857</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3564</v>
+        <v>-0.1517</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.421</v>
+        <v>-0.2339</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9988</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.2402</v>
+        <v>-1.5117</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1935</v>
+        <v>1.0811</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4337</v>
+        <v>-2.5928</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9373</v>
+        <v>-1.9732</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0078</v>
+        <v>0.3868</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9451</v>
+        <v>-2.36</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4023</v>
+        <v>-0.3013</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6859</v>
+        <v>1.1295</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2836</v>
+        <v>-1.4308</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3395</v>
+        <v>-1.6718</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6781</v>
+        <v>-0.7427</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6615</v>
+        <v>-0.9292</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0561</v>
+        <v>0.7196</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9663</v>
+        <v>0.6946</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0898</v>
+        <v>0.025</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5549</v>
+        <v>-1.8249</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.5549</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>M. JUAN SEVILLANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3202</v>
+        <v>-1.837</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5694</v>
+        <v>0.4407</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8896</v>
+        <v>-2.2777</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9732</v>
+        <v>-0.2129</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3868</v>
+        <v>0.6714</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.36</v>
+        <v>-0.8843</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3013</v>
+        <v>2.4703</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1295</v>
+        <v>1.8901</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4308</v>
+        <v>0.5803</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6718</v>
+        <v>-2.6832</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7427</v>
+        <v>-1.2187</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9292</v>
+        <v>-1.4646</v>
       </c>
       <c r="P17" t="n">
+        <v>-1.5668</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-3.1336</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.5668</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-0.1958</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.7626</v>
-      </c>
       <c r="S17" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.8263</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1829</v>
+        <v>1.1039</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2718</v>
+        <v>-0.2776</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8249</v>
+        <v>-0.8837</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7086</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. JUAN SEVILLANO</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3966</v>
+        <v>-2.5739</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3383</v>
+        <v>-0.1135</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7349</v>
+        <v>-2.4604</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2129</v>
+        <v>-0.9373</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6714</v>
+        <v>1.0078</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8843</v>
+        <v>-1.9451</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4703</v>
+        <v>0.4023</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8901</v>
+        <v>1.6859</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5803</v>
+        <v>-1.2836</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6832</v>
+        <v>-1.3395</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2187</v>
+        <v>-0.6781</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4646</v>
+        <v>-0.6615</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1336</v>
+        <v>-1.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2668</v>
+        <v>0.7224</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0016</v>
+        <v>0.6593</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7348</v>
+        <v>0.0631</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8837</v>
+        <v>-2.5549</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8837</v>
+        <v>-2.5549</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9046</v>
+        <v>-3.7534</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3338</v>
+        <v>-1.1291</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5708</v>
+        <v>-2.6243</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0262</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2909</v>
+        <v>-0.1397</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1249</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.763</v>
+        <v>-4.2172</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0558</v>
+        <v>-0.6465</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7072</v>
+        <v>-3.5707</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1578</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2376</v>
+        <v>0.7834</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0371</v>
+        <v>0.3723</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2747</v>
+        <v>0.4111</v>
       </c>
       <c r="V20" t="n">
         <v>1.0949</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.4256</v>
+        <v>-7.5989</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0047</v>
+        <v>-4.3117</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4209</v>
+        <v>-3.2872</v>
       </c>
       <c r="G21" t="n">
         <v>-5.4636</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1597</v>
+        <v>-0.0137</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2841</v>
+        <v>-0.0229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1244</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3383</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.980699999999999</v>
+        <v>-9.196000000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>8.5014</v>
+        <v>8.6037</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.4821</v>
+        <v>-17.7999</v>
       </c>
       <c r="G22" t="n">
         <v>-6.000099999999999</v>
@@ -2170,16 +2170,16 @@
         <v>10.7714</v>
       </c>
       <c r="S22" t="n">
-        <v>4.214099999999999</v>
+        <v>4.9985</v>
       </c>
       <c r="T22" t="n">
-        <v>4.0846</v>
+        <v>4.187</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1295999999999999</v>
+        <v>0.8118</v>
       </c>
       <c r="V22" t="n">
-        <v>-5.257099999999999</v>
+        <v>-5.2571</v>
       </c>
       <c r="W22" t="n">
         <v>4.027799999999999</v>
